--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91535</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34292-2025 artfynd.xlsx
+++ b/artfynd/A 34292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128544603</v>
       </c>
       <c r="B2" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128544644</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
